--- a/DataTables/DetailText/剧情/完书.xlsx
+++ b/DataTables/DetailText/剧情/完书.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D57D102-4BF1-473E-9A8F-D539B605396E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23109596-1B31-4F53-AF26-5F7ABACF647A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="750" yWindow="2100" windowWidth="21600" windowHeight="11423" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,23 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="57">
   <si>
     <t>StoryID</t>
   </si>
@@ -105,9 +94,6 @@
     <t>SortIndex</t>
   </si>
   <si>
-    <t>night</t>
-  </si>
-  <si>
     <t>ClinicNpcPortraitPath</t>
   </si>
   <si>
@@ -139,10 +125,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>night_end</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>完书</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -322,10 +304,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>李东璧花费27年，历经三次改写，至万历六年终于完成著作。参考800多种书籍，多次去各地实地考察，采集样本，耗费大量心血。全书共52卷，载药1892种，方剂11096首，插图图1109幅约190万字。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -394,7 +372,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>谁能愿意出版这种卖不出去的医书呢</t>
+      <t>谁能愿意出版这种不赚钱的医书呢</t>
     </r>
     <r>
       <rPr>
@@ -407,17 +385,1166 @@
       <t>？</t>
     </r>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>父</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>亲</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>恩</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>师顾</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>老先生的世交王世</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>贞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>，乃是当世文</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>坛领</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>袖，若是能</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>让</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>他帮忙</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>给书</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>写一个序</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>，肯定有书商愿意出版。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>是个好主意，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>过</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>几日我就启程拜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>访</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>王先生。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>李东璧来到江苏太仓王世贞府</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>久闻李老先生大名，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>远</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>道而来有失</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>远</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>迎。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>老朽今日来是有一事相求，望王先生成全。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>王世贞</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>愿闻其详。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>部医</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>书</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>是老朽</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>行医三十年所校定的本草集，想</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>让</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>它能刻</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>录</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>成</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>书为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>后世所用，但</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>苦于无人愿出版此</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>书</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>若能得当时文坛第一人王先生</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>此</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>书</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>写一段序，肯定会有闻名而来的人让老夫了却毕生心愿。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>此事在下</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>义</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>不容辞，但王某人需拜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>读</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>完老先生著作方可写序</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>，还请见谅。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>哎呀，那老朽就多谢先生了。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>李东璧花费27年，历经三次改写，至万历六年终于完成著作。参考800多种书籍，多次去各地实地考察，采集样本，耗费大量心血。全书共52卷，载药1892种，方剂11096首，插图图1109幅，约190万字。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>此帝王之秘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>箓</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，臣民之重宝。兹集也，藏之深山石室，无当。盖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>锲</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>之，以共天下后世味太玄如子云者。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>一晃又是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>许</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>多年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>过</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>去，王世</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>贞终</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>于</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>读</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>完，并</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>此</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>书</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>写了序。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>万</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>历</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>二十四年，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>部耗尽他一生心血的医</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>书终于</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>刊印</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>发</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>售</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>珍，荆楚鄙人也。幼多羸疾，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>质</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>成</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>钝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>椎。僭纂述之权，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>岁历</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>三十稔，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>书</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>考八百余家，稿凡三易，复者芟之，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>阙</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>者</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>缉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>之，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>讹</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>者</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>绳</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>之。旧本一千五百二十八种，今增</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>药</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>三百七十四种，分</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>一十六部，著成五十二卷，僭名曰本草</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>纲</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>目。——【明】李</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>珍《本草</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>纲</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>目》</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>万</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>历</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>二十一年李</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>东</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>壁病逝，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>终</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年76</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>岁…</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>clinic</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>scene_enter</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -431,7 +1558,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -452,7 +1579,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -476,6 +1603,13 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
     </font>
@@ -539,7 +1673,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -595,9 +1729,18 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -876,27 +2019,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.86328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -913,31 +2056,31 @@
         <v>18</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G1" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="12" t="s">
         <v>26</v>
-      </c>
-      <c r="H1" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" s="12" t="s">
-        <v>27</v>
       </c>
       <c r="J1" s="13" t="s">
         <v>16</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L1" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M1" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="N1" s="15" t="s">
         <v>24</v>
-      </c>
-      <c r="N1" s="15" t="s">
-        <v>25</v>
       </c>
       <c r="O1" s="16" t="s">
         <v>17</v>
@@ -946,19 +2089,19 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16">
       <c r="A2" s="5"/>
       <c r="B2" s="19" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
@@ -976,66 +2119,66 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16">
       <c r="C3" s="10"/>
       <c r="H3" s="14"/>
       <c r="L3" s="18"/>
       <c r="O3" s="11"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16" ht="18.75">
       <c r="C4" s="10"/>
       <c r="H4" s="14"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16" ht="18.75">
       <c r="C5" s="10"/>
       <c r="H5" s="14"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16" ht="18.75">
       <c r="C6" s="10"/>
       <c r="H6" s="14"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16" ht="18.75">
       <c r="C7" s="10"/>
       <c r="H7" s="14"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16" ht="18.75">
       <c r="C8" s="10"/>
       <c r="H8" s="14"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16" ht="18.75">
       <c r="H9" s="14"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:16" ht="18.75">
       <c r="H10" s="14"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:16" ht="18.75">
       <c r="H11" s="14"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:16" ht="18.75">
       <c r="H12" s="14"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:16" ht="18.75">
       <c r="H13" s="14"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:16" ht="18.75">
       <c r="H14" s="14"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:16" ht="18.75">
       <c r="H15" s="14"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:16" ht="18.75">
       <c r="H16" s="14"/>
     </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="8:8" ht="18.75">
       <c r="H17" s="14"/>
     </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="8:8" ht="18.75">
       <c r="H18" s="14"/>
     </row>
-    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="8:8" ht="18.75">
       <c r="H19" s="14"/>
     </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="8:8">
       <c r="H20" s="14"/>
     </row>
   </sheetData>
@@ -1046,21 +2189,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
-  <dimension ref="A1:H15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -1086,7 +2229,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="30">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1099,10 +2242,10 @@
       <c r="F2" s="8"/>
       <c r="G2" s="2"/>
       <c r="H2" s="19" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1110,21 +2253,21 @@
         <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F3" s="8"/>
       <c r="G3" s="2"/>
       <c r="H3" s="20" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1132,21 +2275,21 @@
         <v>7</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>9</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F4" s="8"/>
       <c r="G4" s="2"/>
       <c r="H4" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1154,19 +2297,19 @@
         <v>7</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1174,21 +2317,21 @@
         <v>7</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="20" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1196,111 +2339,275 @@
         <v>7</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H7" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="3"/>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H8" s="21" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="3"/>
+      <c r="B9" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="C9" s="3"/>
       <c r="D9" s="2"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H9" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="2"/>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H10" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="2"/>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H11" s="21" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="2"/>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H12" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="2"/>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H13" s="21" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="2"/>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H14" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="2"/>
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
+      <c r="H15" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="3"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="3"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="3"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="21" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="3"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="54">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="3"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="23" t="s">
+        <v>53</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/DataTables/DetailText/剧情/完书.xlsx
+++ b/DataTables/DetailText/剧情/完书.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23109596-1B31-4F53-AF26-5F7ABACF647A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C55E2FDD-6967-4407-97A7-15AFD04D5FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="750" yWindow="2100" windowWidth="21600" windowHeight="11423" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,6 +21,17 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -1532,8 +1543,7 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>scene_enter</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <t>day_reputation_over</t>
   </si>
 </sst>
 </file>
@@ -1544,7 +1554,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1558,7 +1568,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1579,7 +1589,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1740,7 +1750,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2019,24 +2029,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.86328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -2125,57 +2135,57 @@
       <c r="L3" s="18"/>
       <c r="O3" s="11"/>
     </row>
-    <row r="4" spans="1:16" ht="18.75">
+    <row r="4" spans="1:16">
       <c r="C4" s="10"/>
       <c r="H4" s="14"/>
     </row>
-    <row r="5" spans="1:16" ht="18.75">
+    <row r="5" spans="1:16">
       <c r="C5" s="10"/>
       <c r="H5" s="14"/>
     </row>
-    <row r="6" spans="1:16" ht="18.75">
+    <row r="6" spans="1:16">
       <c r="C6" s="10"/>
       <c r="H6" s="14"/>
     </row>
-    <row r="7" spans="1:16" ht="18.75">
+    <row r="7" spans="1:16">
       <c r="C7" s="10"/>
       <c r="H7" s="14"/>
     </row>
-    <row r="8" spans="1:16" ht="18.75">
+    <row r="8" spans="1:16">
       <c r="C8" s="10"/>
       <c r="H8" s="14"/>
     </row>
-    <row r="9" spans="1:16" ht="18.75">
+    <row r="9" spans="1:16">
       <c r="H9" s="14"/>
     </row>
-    <row r="10" spans="1:16" ht="18.75">
+    <row r="10" spans="1:16">
       <c r="H10" s="14"/>
     </row>
-    <row r="11" spans="1:16" ht="18.75">
+    <row r="11" spans="1:16">
       <c r="H11" s="14"/>
     </row>
-    <row r="12" spans="1:16" ht="18.75">
+    <row r="12" spans="1:16">
       <c r="H12" s="14"/>
     </row>
-    <row r="13" spans="1:16" ht="18.75">
+    <row r="13" spans="1:16">
       <c r="H13" s="14"/>
     </row>
-    <row r="14" spans="1:16" ht="18.75">
+    <row r="14" spans="1:16">
       <c r="H14" s="14"/>
     </row>
-    <row r="15" spans="1:16" ht="18.75">
+    <row r="15" spans="1:16">
       <c r="H15" s="14"/>
     </row>
-    <row r="16" spans="1:16" ht="18.75">
+    <row r="16" spans="1:16">
       <c r="H16" s="14"/>
     </row>
-    <row r="17" spans="8:8" ht="18.75">
+    <row r="17" spans="8:8">
       <c r="H17" s="14"/>
     </row>
-    <row r="18" spans="8:8" ht="18.75">
+    <row r="18" spans="8:8">
       <c r="H18" s="14"/>
     </row>
-    <row r="19" spans="8:8" ht="18.75">
+    <row r="19" spans="8:8">
       <c r="H19" s="14"/>
     </row>
     <row r="20" spans="8:8">
@@ -2192,14 +2202,14 @@
   <dimension ref="A1:H21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -2229,7 +2239,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="30">
+    <row r="2" spans="1:8" ht="33">
       <c r="A2" s="1">
         <v>1</v>
       </c>

--- a/DataTables/DetailText/剧情/完书.xlsx
+++ b/DataTables/DetailText/剧情/完书.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C55E2FDD-6967-4407-97A7-15AFD04D5FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34FC6A20-A67D-4F16-8A99-B600A47410D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="21600" windowHeight="11423" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,26 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="57">
-  <si>
-    <t>StoryID</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="61">
   <si>
     <t>LineIndex</t>
   </si>
@@ -83,57 +69,10 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>StoryName</t>
-  </si>
-  <si>
-    <t>TriggerType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TriggerScene</t>
-  </si>
-  <si>
-    <t>NpcID</t>
-  </si>
-  <si>
     <t>PlayOnce</t>
   </si>
   <si>
-    <t>ReturnScene</t>
-  </si>
-  <si>
     <t>SortIndex</t>
-  </si>
-  <si>
-    <t>ClinicNpcPortraitPath</t>
-  </si>
-  <si>
-    <t>TriggerStoryID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TriggerDay</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Reputation</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Experience</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerReputation</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerEntryId</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Disease</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>完书</t>
@@ -1539,22 +1478,106 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>剧情ID</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>剧情名</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发场景</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发天数</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <r>
+      <t>金</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>钱判定</t>
+    </r>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发金钱</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>名望判定</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发名望</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发条目</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发剧情ID</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发治疗结果</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>播放后</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>人物ID</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>疾病</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>人物立绘路径</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>奖励金钱</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>奖励名望</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>奖励心得</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
     <t>clinic</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>day_reputation_over</t>
+  </si>
+  <si>
+    <t>≥</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1568,7 +1591,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1589,20 +1612,12 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Noto Sans JP"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Noto Sans JP"/>
@@ -1623,8 +1638,30 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Noto Sans JP"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1639,20 +1676,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF92D050"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF200"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1683,7 +1722,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1697,9 +1736,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1709,27 +1745,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1748,9 +1770,37 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2028,171 +2078,202 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <dimension ref="A1:T20"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.9296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.06640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.06640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
-      <c r="A1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6" t="s">
+    <row r="1" spans="1:20" s="24" customFormat="1">
+      <c r="A1" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="G1" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="I1" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="J1" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="K1" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="L1" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="M1" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="N1" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="O1" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="P1" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q1" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="R1" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="S1" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="T1" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="6" t="s">
+    </row>
+    <row r="2" spans="1:20" s="24" customFormat="1">
+      <c r="A2" s="25"/>
+      <c r="B2" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="H1" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="I1" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="J1" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="K1" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="M1" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="N1" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="O1" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="P1" s="16" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16">
-      <c r="A2" s="5"/>
-      <c r="B2" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="1" t="b">
+      <c r="C2" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="H2" s="13">
+        <v>2000</v>
+      </c>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="M2" s="25"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="13"/>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="26"/>
+      <c r="S2" s="26" t="b">
         <v>1</v>
       </c>
-      <c r="P2" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16">
-      <c r="C3" s="10"/>
-      <c r="H3" s="14"/>
-      <c r="L3" s="18"/>
-      <c r="O3" s="11"/>
-    </row>
-    <row r="4" spans="1:16">
-      <c r="C4" s="10"/>
-      <c r="H4" s="14"/>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="C5" s="10"/>
-      <c r="H5" s="14"/>
-    </row>
-    <row r="6" spans="1:16">
-      <c r="C6" s="10"/>
-      <c r="H6" s="14"/>
-    </row>
-    <row r="7" spans="1:16">
-      <c r="C7" s="10"/>
-      <c r="H7" s="14"/>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="C8" s="10"/>
-      <c r="H8" s="14"/>
-    </row>
-    <row r="9" spans="1:16">
-      <c r="H9" s="14"/>
-    </row>
-    <row r="10" spans="1:16">
-      <c r="H10" s="14"/>
-    </row>
-    <row r="11" spans="1:16">
-      <c r="H11" s="14"/>
-    </row>
-    <row r="12" spans="1:16">
-      <c r="H12" s="14"/>
-    </row>
-    <row r="13" spans="1:16">
-      <c r="H13" s="14"/>
-    </row>
-    <row r="14" spans="1:16">
-      <c r="H14" s="14"/>
-    </row>
-    <row r="15" spans="1:16">
-      <c r="H15" s="14"/>
-    </row>
-    <row r="16" spans="1:16">
-      <c r="H16" s="14"/>
+      <c r="T2" s="26"/>
+    </row>
+    <row r="3" spans="1:20">
+      <c r="C3" s="8"/>
+      <c r="H3" s="10"/>
+      <c r="L3" s="11"/>
+      <c r="O3" s="9"/>
+    </row>
+    <row r="4" spans="1:20">
+      <c r="C4" s="8"/>
+      <c r="H4" s="10"/>
+    </row>
+    <row r="5" spans="1:20">
+      <c r="C5" s="8"/>
+      <c r="H5" s="10"/>
+    </row>
+    <row r="6" spans="1:20">
+      <c r="C6" s="8"/>
+      <c r="H6" s="10"/>
+    </row>
+    <row r="7" spans="1:20">
+      <c r="C7" s="8"/>
+      <c r="H7" s="10"/>
+    </row>
+    <row r="8" spans="1:20">
+      <c r="C8" s="8"/>
+      <c r="H8" s="10"/>
+    </row>
+    <row r="9" spans="1:20">
+      <c r="H9" s="10"/>
+    </row>
+    <row r="10" spans="1:20">
+      <c r="H10" s="10"/>
+    </row>
+    <row r="11" spans="1:20">
+      <c r="H11" s="10"/>
+    </row>
+    <row r="12" spans="1:20">
+      <c r="H12" s="10"/>
+    </row>
+    <row r="13" spans="1:20">
+      <c r="H13" s="10"/>
+    </row>
+    <row r="14" spans="1:20">
+      <c r="H14" s="10"/>
+    </row>
+    <row r="15" spans="1:20">
+      <c r="H15" s="10"/>
+    </row>
+    <row r="16" spans="1:20">
+      <c r="H16" s="10"/>
     </row>
     <row r="17" spans="8:8">
-      <c r="H17" s="14"/>
+      <c r="H17" s="10"/>
     </row>
     <row r="18" spans="8:8">
-      <c r="H18" s="14"/>
+      <c r="H18" s="10"/>
     </row>
     <row r="19" spans="8:8">
-      <c r="H19" s="14"/>
+      <c r="H19" s="10"/>
     </row>
     <row r="20" spans="8:8">
-      <c r="H20" s="14"/>
+      <c r="H20" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
+  <dataValidations count="5">
+    <dataValidation type="list" sqref="C2" xr:uid="{8700D4A4-3046-451F-B764-47BFBF556E16}">
+      <formula1>"clinic,night,night_end"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="E2 G2" xr:uid="{DA4BB2E6-3E69-4D62-B8E4-A5690E3C56F4}">
+      <formula1>"≥,≤"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="L2" xr:uid="{EBBABA4C-CD4E-451B-A8B4-A04EBB149E59}">
+      <formula1>"clinic,night,end_game"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="S2" xr:uid="{A1C87CF0-117A-4149-9D93-BCAD28054DE6}">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="K2" xr:uid="{BCE7DB1F-254E-4F3D-B8C9-76FEDB8BBF05}">
+      <formula1>"cured,failed"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2202,57 +2283,57 @@
   <dimension ref="A1:H21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="33">
+    </row>
+    <row r="2" spans="1:8" ht="30">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="8"/>
+      <c r="F2" s="7"/>
       <c r="G2" s="2"/>
-      <c r="H2" s="19" t="s">
-        <v>49</v>
+      <c r="H2" s="12" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -2260,21 +2341,21 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F3" s="8"/>
+        <v>16</v>
+      </c>
+      <c r="F3" s="7"/>
       <c r="G3" s="2"/>
-      <c r="H3" s="20" t="s">
-        <v>31</v>
+      <c r="H3" s="13" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -2282,21 +2363,21 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>9</v>
+        <v>18</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" s="8"/>
+        <v>16</v>
+      </c>
+      <c r="F4" s="7"/>
       <c r="G4" s="2"/>
       <c r="H4" s="1" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -2304,19 +2385,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="1" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -2324,21 +2405,21 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
-      <c r="H6" s="20" t="s">
-        <v>37</v>
+      <c r="H6" s="13" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -2346,19 +2427,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -2366,21 +2447,21 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
-      <c r="H8" s="21" t="s">
-        <v>39</v>
+      <c r="H8" s="14" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -2388,7 +2469,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="2"/>
@@ -2396,7 +2477,7 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -2404,19 +2485,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -2424,19 +2505,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
-      <c r="H11" s="21" t="s">
-        <v>42</v>
+      <c r="H11" s="14" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -2444,19 +2525,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -2464,19 +2545,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
-      <c r="H13" s="21" t="s">
-        <v>45</v>
+      <c r="H13" s="14" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -2484,19 +2565,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -2504,19 +2585,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -2524,19 +2605,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -2544,7 +2625,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="2"/>
@@ -2552,7 +2633,7 @@
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -2560,15 +2641,15 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="2"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
-      <c r="H18" s="22" t="s">
-        <v>50</v>
+      <c r="H18" s="15" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -2576,15 +2657,15 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="2"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
-      <c r="H19" s="21" t="s">
-        <v>54</v>
+      <c r="H19" s="14" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -2592,7 +2673,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="2"/>
@@ -2600,7 +2681,7 @@
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="54">
@@ -2608,15 +2689,15 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C21" s="3"/>
       <c r="D21" s="2"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
-      <c r="H21" s="23" t="s">
-        <v>53</v>
+      <c r="H21" s="16" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
